--- a/data/leermiddelen-pelckmans.xlsx
+++ b/data/leermiddelen-pelckmans.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA381FE0-7F34-2D49-BA09-B9AE521A6152}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{060D8FDF-12F9-400A-BF56-99AC35459CA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1100" yWindow="500" windowWidth="37300" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Leermiddel" sheetId="4" r:id="rId1"/>
@@ -142,7 +142,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -156,6 +156,14 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -205,22 +213,93 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="16">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE0E0E0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -231,6 +310,36 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{09522D8B-501B-444F-BABA-A8076BD507DF}" name="Table1" displayName="Table1" ref="A1:U5" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
+  <autoFilter ref="A1:U5" xr:uid="{09522D8B-501B-444F-BABA-A8076BD507DF}"/>
+  <tableColumns count="21">
+    <tableColumn id="1" xr3:uid="{26366652-CB76-4D4C-878C-C362F58F93D7}" name="CODE"/>
+    <tableColumn id="2" xr3:uid="{0A959A3D-6826-467C-B35F-F62E5DD3A05F}" name="beschrijving" dataDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{0AA647D7-2BF1-45A0-829B-A7FF556C6549}" name="instructie" dataDxfId="14"/>
+    <tableColumn id="4" xr3:uid="{44CAC3F0-F6F7-44D2-B936-0545ED2C47D6}" name="naam"/>
+    <tableColumn id="5" xr3:uid="{1EB4E457-EE81-46B0-85A4-48C6B1690335}" name="vereiste" dataDxfId="13"/>
+    <tableColumn id="6" xr3:uid="{6949DC9B-F593-4EF3-A01B-D9EE92134F38}" name="benodigdMateriaal" dataDxfId="12"/>
+    <tableColumn id="7" xr3:uid="{B4FC4B21-0697-4800-B08D-A3E0AF668CA0}" name="sleutelwoord" dataDxfId="11"/>
+    <tableColumn id="8" xr3:uid="{F392E7F2-1BBB-4D07-B4D2-3B7A372E4E17}" name="onderwerp"/>
+    <tableColumn id="9" xr3:uid="{928ADCA4-0748-43C9-8144-7093097CDD0B}" name="toegankelijkheid" dataDxfId="10"/>
+    <tableColumn id="10" xr3:uid="{EDE9DEC1-49BB-4580-9D8D-99FA0759875B}" name="type"/>
+    <tableColumn id="11" xr3:uid="{C979CE61-531A-4AAF-A510-C0026B9F1EB4}" name="interactieType" dataDxfId="9"/>
+    <tableColumn id="12" xr3:uid="{9399B0B6-1CF1-413B-9889-D43A8685D055}" name="instructietaal" dataDxfId="8"/>
+    <tableColumn id="13" xr3:uid="{C8EBC8F7-42A0-4935-9CFC-70E7E4DC2B8D}" name="resultaat" dataDxfId="7"/>
+    <tableColumn id="14" xr3:uid="{42595975-0E41-469F-89F9-EC06F4A13473}" name="niveau"/>
+    <tableColumn id="15" xr3:uid="{28E16E37-C770-42E7-AE23-3C6516E0CE05}" name="kost" dataDxfId="6"/>
+    <tableColumn id="16" xr3:uid="{D2821F49-1A3D-4444-8D8F-3E31972D65A0}" name="formaat" dataDxfId="5"/>
+    <tableColumn id="17" xr3:uid="{F48DE170-4111-46A7-84CE-9879C4C767DA}" name="competentie" dataDxfId="4"/>
+    <tableColumn id="18" xr3:uid="{B373A0C8-1D2D-40F3-9074-D46631FA08F4}" name="bron"/>
+    <tableColumn id="19" xr3:uid="{3D84B7D2-0968-4730-9CB1-604D9787BE60}" name="dient"/>
+    <tableColumn id="20" xr3:uid="{92ED0766-91EF-466A-B1FF-64A5C9EB7140}" name="isLidVan" dataDxfId="3"/>
+    <tableColumn id="21" xr3:uid="{1326269A-97FC-42B9-B9F7-AB95E00B3C85}" name="bestaatUit" dataDxfId="2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -556,202 +665,205 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:U5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="40" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="40" style="1" customWidth="1"/>
-    <col min="5" max="5" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="40" style="1" customWidth="1"/>
-    <col min="9" max="9" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="40" style="1" customWidth="1"/>
-    <col min="15" max="15" width="4.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="40" style="1" customWidth="1"/>
-    <col min="19" max="19" width="40" customWidth="1"/>
-    <col min="20" max="20" width="7.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="37.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="54.7109375" customWidth="1"/>
+    <col min="20" max="20" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:21" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" s="5" t="s">
         <v>17</v>
       </c>
       <c r="S1" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="U1" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="2" t="s">
         <v>34</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="N2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="R2" s="4" t="s">
+      <c r="R2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="S2" s="4" t="s">
+      <c r="S2" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="3" t="s">
         <v>34</v>
       </c>
       <c r="L3" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="N3" s="5" t="s">
+      <c r="N3" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="R3" s="5" t="s">
+      <c r="R3" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="S3" s="5" t="s">
+      <c r="S3" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:21" ht="16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="J4" s="2" t="s">
         <v>34</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="N4" s="4" t="s">
+      <c r="N4" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="R4" s="4" t="s">
+      <c r="R4" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="S4" s="4" t="s">
+      <c r="S4" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H5" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="J5" s="5" t="s">
+      <c r="J5" s="3" t="s">
         <v>34</v>
       </c>
       <c r="L5" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="N5" s="5" t="s">
+      <c r="N5" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="R5" s="5" t="s">
+      <c r="R5" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="S5" s="5" t="s">
+      <c r="S5" s="3" t="s">
         <v>35</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>